--- a/content/table2-3.xlsx
+++ b/content/table2-3.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/二下题库/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c72363082c40911d/doc/Grand Homes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{247418F4-F786-4429-ADF0-F57F7D91E882}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D6C097A-0704-4BDB-A721-31EBF73B0081}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5790" yWindow="2295" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="93">
   <si>
     <t>Round1</t>
   </si>
@@ -366,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -376,6 +377,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -658,15 +662,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
   <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -677,87 +681,87 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -768,7 +772,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -776,7 +780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -784,7 +788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -792,7 +796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -800,7 +804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -808,13 +812,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>20</v>
       </c>
@@ -822,7 +826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
@@ -830,7 +834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -838,7 +842,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
@@ -846,7 +850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>16</v>
       </c>
@@ -854,7 +858,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>25</v>
       </c>
@@ -862,7 +866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>37</v>
       </c>
@@ -873,7 +877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
@@ -881,7 +885,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
@@ -889,7 +893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
@@ -897,7 +901,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
@@ -905,7 +909,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>39</v>
       </c>
@@ -916,7 +920,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>40</v>
       </c>
@@ -924,7 +928,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>41</v>
       </c>
@@ -932,7 +936,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>42</v>
       </c>
@@ -940,7 +944,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -948,7 +952,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>50</v>
       </c>
@@ -959,7 +963,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>51</v>
       </c>
@@ -967,7 +971,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>52</v>
       </c>
@@ -975,7 +979,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>53</v>
       </c>
@@ -983,7 +987,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>54</v>
       </c>
@@ -991,7 +995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>61</v>
       </c>
@@ -1005,7 +1009,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>62</v>
       </c>
@@ -1016,7 +1020,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>64</v>
       </c>
@@ -1027,7 +1031,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>63</v>
       </c>
@@ -1038,7 +1042,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>65</v>
       </c>
@@ -1048,6 +1052,98 @@
       <c r="C50" s="4" t="s">
         <v>74</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACDE2F0-DCF4-4E0B-AD41-CFE00F331807}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
